--- a/afruheritage-platform/uat-package/PRODUCT_CAPABILITY_MATRIX.xlsx
+++ b/afruheritage-platform/uat-package/PRODUCT_CAPABILITY_MATRIX.xlsx
@@ -34,7 +34,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -59,11 +59,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FEE2E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FECACA"/>
       </patternFill>
     </fill>
     <fill>
@@ -99,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -123,9 +118,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -874,54 +866,54 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Shipment status notifications</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Customers informed of status changes</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>PO: core gap — customers should receive updates</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>DEFECTIVE — send_shipment_status_update_email + delivered email exist and ARE wired in record_tracking_event (shipment_service.py:948-968), but the UI transition endpoint (POST /transition) bypasses that path and sends nothing; recipient is tenant contact only, not end customer; send failures swallowed to logs</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED — 2026-10-12: transition endpoint now calls shared notify_shipment_status_change; D-03 both recipients (tenant contact + receiver_email, new optional field) notified; real mail.tm inbox delivery proven on transition AND event paths; email link fixed to public /track?tracking_number=; cross-tenant blocked 403 (P22)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Customers get zero shipment updates today</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Customers previously got zero shipment updates</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>Wire notifications into transition path + define recipient (customer vs tenant) + surface failures</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Fix before launch</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>YES — who receives notifications (tenant owner, end customer, both)?</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Done — see PHASE1_EVIDENCE.md</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Fixed before launch</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1030,52 +1022,52 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Central Afruheritage platform support</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Platform-level support independent of tenant tickets</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>PO: core gap</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>MISSING as ticket channel — public tickets require tenant_id (422 without); apex /support honestly explains tenant-routing. Help assistant + branded email exist as informal channels</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>High if PO requires central support at launch</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>No channel for platform-level issues (billing disputes, onboarding help)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Admin tickets view covers all tenants — intake path missing only</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Add platform-scope ticket path (tenant_id optional) + apex intake form, or stand up support@ workflow</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>PO decision</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>YES — is central ticket intake required at launch?</t>
         </is>
@@ -1134,52 +1126,52 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Live payment collection (charges)</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Real-money subscription payments</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>PO: commercial blocker for paid launch</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>IMPLEMENTED-UNVERIFIED — Paystack + Flutterwave clients exist (initialize/verify, webhooks, authorization_url flow); never exercised end-to-end with real keys in UAT</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>Depends on launch model — required if charging at launch</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Cannot collect revenue if broken</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Payments admin list (WORKING); refund/dispute MISSING</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>End-to-end charge test with live keys; decide refund/dispute scope</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>PO decision</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>YES — go-live with paid billing now, or trial-only launch?</t>
         </is>
@@ -1602,52 +1594,52 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Native mobile app</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>iOS/Android apps</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Roadmap</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>UNSUPPORTED — responsive web only</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>PO: reasonable deferral</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>None — web works on mobile browsers</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>Post-launch/roadmap</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Confirm deferral</t>
         </is>
@@ -1706,52 +1698,52 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Admin audit logging</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Immutable record of admin actions</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>AGENT.md audit mandate; PO requirement</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>PARTIAL — admin_audit_logs records admin.login + runners.listed; CP-proxied mutations (KYC approve, flag toggle, ticket status, tenant/billing actions) write no audit row</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED — 2026-10-12: audited_admin_mutation wraps all sentinel write routes; durable rows carry actor/action/entity/params/outcome incl. outcome=error on rejected mutations (live-verified ticket/KYC/flag mutations)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Core for supportability</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Diagnostics audit view exists</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Audit middleware on all sentinel write routes</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>Before launch</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Done — see PHASE1_EVIDENCE.md</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Fixed before launch</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1914,52 +1906,52 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>Branded sender domain (@afruheritage.com email)</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Customer emails from platform domain</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Branding/trust; PO requirement</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>BLOCKED — provider account rejects @afruheritage.com senders; mail sends as advisory@emidentity.com; SPF strict, no DKIM, DMARC p=none</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>High for brand trust at public launch</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>Customers see non-branded sender</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>Provision sender domain + publish DKIM + tighten DMARC (ops action)</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>Before public pilot</t>
         </is>
       </c>
-      <c r="J28" s="9" t="inlineStr">
+      <c r="J28" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1976,7 +1968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1986,22 +1978,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Options</t>
         </is>
@@ -2053,17 +2045,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YES — who receives notifications (tenant owner, end customer, both)?</t>
+          <t>YES — is central ticket intake required at launch?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shipment status notifications: DEFECTIVE — send_shipment_status_update_email + delivered email exist and ARE wired in record_tracking_event (shipment_service.py:948-968), </t>
+          <t>Central Afruheritage platform support: MISSING as ticket channel — public tickets require tenant_id (422 without); apex /support honestly explains tenant-routing. Help assistant +</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fix before launch / launch scope</t>
+          <t>PO decision / launch scope</t>
         </is>
       </c>
     </row>
@@ -2073,12 +2065,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YES — is central ticket intake required at launch?</t>
+          <t>YES — go-live with paid billing now, or trial-only launch?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Central Afruheritage platform support: MISSING as ticket channel — public tickets require tenant_id (422 without); apex /support honestly explains tenant-routing. Help assistant +</t>
+          <t>Live payment collection (charges): IMPLEMENTED-UNVERIFIED — Paystack + Flutterwave clients exist (initialize/verify, webhooks, authorization_url flow); never exercised end-to-</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2093,12 +2085,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YES — go-live with paid billing now, or trial-only launch?</t>
+          <t>YES — is CRM activity UI required at launch?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Live payment collection (charges): IMPLEMENTED-UNVERIFIED — Paystack + Flutterwave clients exist (initialize/verify, webhooks, authorization_url flow); never exercised end-to-</t>
+          <t>CRM activity history: PARTIAL — CrmActivity model + GET/POST /customers/{id}/activities endpoints exist; no UI surface for activities</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2113,17 +2105,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YES — is CRM activity UI required at launch?</t>
+          <t>Confirm deferral</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CRM activity history: PARTIAL — CrmActivity model + GET/POST /customers/{id}/activities endpoints exist; no UI surface for activities</t>
+          <t>Additional storefront templates (5 demos): PARTIAL — previewable, publish-blocked (fake-content themes now degrade to generic shell)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PO decision / launch scope</t>
+          <t>Post-launch / launch scope</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2130,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Additional storefront templates (5 demos): PARTIAL — previewable, publish-blocked (fake-content themes now degrade to generic shell)</t>
+          <t>Custom domains: PARTIAL — custom_domain_events + domains admin exist; end-to-end custom-domain flow unverified</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2153,17 +2145,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Confirm deferral</t>
+          <t>YES — does Afruheritage sell warehouse management?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Custom domains: PARTIAL — custom_domain_events + domains admin exist; end-to-end custom-domain flow unverified</t>
+          <t>Warehouse operations: MISSING — no implementation found; not in customer nav</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Post-launch / launch scope</t>
+          <t>PO decision / launch scope</t>
         </is>
       </c>
     </row>
@@ -2173,17 +2165,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YES — does Afruheritage sell warehouse management?</t>
+          <t>Confirm basic-counts-only is acceptable</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Warehouse operations: MISSING — no implementation found; not in customer nav</t>
+          <t>Dedicated analytics dashboards: PARTIAL — basic operational stats exist (tenant dashboard endpoint, Sentinel analytics: real users/tenants/shipments/revenue/KYC counts); no</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PO decision / launch scope</t>
+          <t>Post-launch / launch scope</t>
         </is>
       </c>
     </row>
@@ -2193,17 +2185,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Confirm basic-counts-only is acceptable</t>
+          <t>Confirm deferral</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dedicated analytics dashboards: PARTIAL — basic operational stats exist (tenant dashboard endpoint, Sentinel analytics: real users/tenants/shipments/revenue/KYC counts); no</t>
+          <t>Native mobile app: UNSUPPORTED — responsive web only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Post-launch / launch scope</t>
+          <t>Post-launch/roadmap / launch scope</t>
         </is>
       </c>
     </row>
@@ -2213,35 +2205,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Confirm deferral</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Native mobile app: UNSUPPORTED — responsive web only</t>
+          <t>Feature flags — tenant scope: PARTIAL — global flags work (verified toggle+persist); per-tenant flag endpoint returns CP 404</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
-        <is>
-          <t>Post-launch/roadmap / launch scope</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Confirm</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Feature flags — tenant scope: PARTIAL — global flags work (verified toggle+persist); per-tenant flag endpoint returns CP 404</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
         <is>
           <t>Post-launch / launch scope</t>
         </is>

--- a/afruheritage-platform/uat-package/PRODUCT_CAPABILITY_MATRIX.xlsx
+++ b/afruheritage-platform/uat-package/PRODUCT_CAPABILITY_MATRIX.xlsx
@@ -722,42 +722,42 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AGENT.md vendor ops; PO: challenge deferral</t>
+          <t>PO D-01 ratified — platform marketplace model</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>PARTIAL — FULL backend exists: POST /vendors/register (public, rate-limited), documents, availability, marketplace match, bookings accept/reject, admin review+suspend. NO customer/vendor-facing UI built</t>
+          <t>PARTIAL — vendor identity foundation VERIFIED (membership auth, Sentinel approve/link/suspend, /me portal APIs, booking isolation). Registration+booking flows work via API; vendor portal UI still outstanding</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>PO decision — is marketplace part of launch model?</t>
+          <t>PO ruled: complete marketplace — platform-global vendors, tenant-scoped bookings</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Vendors cannot self-onboard via UI; API-only path</t>
+          <t>Vendor portal UI not yet built</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Vendor pages: list/review/suspend (WORKING)</t>
+          <t>Vendor pages: list/review/suspend/membership-link (WORKING + audited)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Build vendor registration page + vendor portal/dashboard UI + tenant marketplace UI</t>
+          <t>Build vendor portal UI + tenant marketplace UI</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>PO decision</t>
+          <t>Under implementation</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>YES — include vendors at launch, or approve deferral?</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>VERIFIED — 2026-10-12: audited_admin_mutation wraps all sentinel write routes; durable rows carry actor/action/entity/params/outcome incl. outcome=error on rejected mutations (live-verified ticket/KYC/flag mutations)</t>
+          <t>VERIFIED — 2026-10-12: all sentinel writes audited; append-only enforced at DB layer (UPDATE/DELETE/TRUNCATE triggers); fail-closed on sensitive mutations (attempt row first, 503+reject on audit-store failure); atomic business+audit commits on same-DB mutations</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1750,54 +1750,54 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Feature flags — tenant scope</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Per-tenant feature entitlements</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Operational control</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>PARTIAL — global flags work (verified toggle+persist); per-tenant flag endpoint returns CP 404</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED — 2026-10-12: governed overrides live (lock→override→plan precedence); grant/revoke/expiry/reason via Sentinel tenant-feature assignments; grant guard blocks unimplemented features (409); resolution live-verified grant+revoke+expiry</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Cannot differentiate tenant features</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Feature Flags page (global WORKING)</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Implement CP tenant-flag endpoints</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>Post-launch</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>Confirm</t>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Control Center tenant-features + Feature Flags pages (WORKING, atomic-audited)</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Done — see PHASE1_EVIDENCE.md Round 2</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Fixed before launch</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2005,17 +2005,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YES — include vendors at launch, or approve deferral?</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vendor registration + marketplace: PARTIAL — FULL backend exists: POST /vendors/register (public, rate-limited), documents, availability, marketplace match, bookings accept/re</t>
+          <t>Vendor registration + marketplace: PARTIAL — vendor identity foundation VERIFIED (membership auth, Sentinel approve/link/suspend, /me portal APIs, booking isolation). Registra</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PO decision / launch scope</t>
+          <t>Under implementation / launch scope</t>
         </is>
       </c>
     </row>
@@ -2196,26 +2196,6 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>Post-launch/roadmap / launch scope</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Confirm</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Feature flags — tenant scope: PARTIAL — global flags work (verified toggle+persist); per-tenant flag endpoint returns CP 404</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Post-launch / launch scope</t>
         </is>
       </c>
     </row>

--- a/afruheritage-platform/uat-package/PRODUCT_CAPABILITY_MATRIX.xlsx
+++ b/afruheritage-platform/uat-package/PRODUCT_CAPABILITY_MATRIX.xlsx
@@ -34,7 +34,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,22 +53,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00BFDBFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BFDBFE"/>
+        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -115,9 +110,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -710,104 +702,104 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Vendor registration + marketplace</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Partner/vendor onboarding, approval, bookings, dispatch</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>PO D-01 ratified — platform marketplace model</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>PARTIAL — vendor identity foundation VERIFIED (membership auth, Sentinel approve/link/suspend, /me portal APIs, booking isolation). Registration+booking flows work via API; vendor portal UI still outstanding</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED — 2026-10-13: full browser journey on deployed prod (P27): public /vendor/register → Sentinel approve → membership link → real invite email → /vendor-accept password setup → vendor login redirects to /vendor → profile/approved dashboard → availability update → tenant booking → vendor accept via UI → /vendor/documents. Membership-only auth, suspended→403, no booked_by PII</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>PO ruled: complete marketplace — platform-global vendors, tenant-scoped bookings</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Vendor portal UI not yet built</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Vendor pages: list/review/suspend/membership-link (WORKING + audited)</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Build vendor portal UI + tenant marketplace UI</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Under implementation</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Driver self-service (sign-in, job updates)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Drivers authenticate and update jobs</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>PO: conditional — needed for driver-operated workflow</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>MISSING — drivers exist only as managed records (Fleetbase proxy); vendor bookings carry driver_name/phone + position tracking, but no driver auth or app</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>PO decision — managed-record fleet mgmt may suffice initially</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Drivers cannot interact with the platform</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>None currently</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Build driver identity + mobile flow if approved</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>PO decision</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>YES — launch with managed drivers only, or require driver portal?</t>
         </is>
@@ -1022,52 +1014,52 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Central Afruheritage platform support</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Platform-level support independent of tenant tickets</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>PO: core gap</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>MISSING as ticket channel — public tickets require tenant_id (422 without); apex /support honestly explains tenant-routing. Help assistant + branded email exist as informal channels</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED — 2026-10-13: apex /support form submits platform-scope tickets (reserved afruheritage-platform tenant alias); public token tracking + guest reply work unauthenticated on apex; Sentinel UI lists/threads/replies/changes status on platform tickets (P28, 14/14); GLPI sync logs durable skipped when unconfigured</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>High if PO requires central support at launch</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>No channel for platform-level issues (billing disputes, onboarding help)</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Admin tickets view covers all tenants — intake path missing only</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Add platform-scope ticket path (tenant_id optional) + apex intake form, or stand up support@ workflow</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>PO decision</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>YES — is central ticket intake required at launch?</t>
         </is>
@@ -1126,52 +1118,52 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Live payment collection (charges)</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Real-money subscription payments</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>PO: commercial blocker for paid launch</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>IMPLEMENTED-UNVERIFIED — Paystack + Flutterwave clients exist (initialize/verify, webhooks, authorization_url flow); never exercised end-to-end with real keys in UAT</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Depends on launch model — required if charging at launch</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>Cannot collect revenue if broken</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>Payments admin list (WORKING); refund/dispute MISSING</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>End-to-end charge test with live keys; decide refund/dispute scope</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>PO decision</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>YES — go-live with paid billing now, or trial-only launch?</t>
         </is>
@@ -1230,52 +1222,52 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>CRM activity history</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Follow-up notes, calls, activity log per customer</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>PO: needs remediation</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>PARTIAL — CrmActivity model + GET/POST /customers/{id}/activities endpoints exist; no UI surface for activities</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED — 2026-10-13: tenant-facing /crm/customers page (create/stage/delete/expandable activity log via real crmApi); crm_customers+crm_activities now tenant_id-scoped (cross-tenant exposure fixed); Sentinel crm-panel rewritten from mock to real API; P28b browser-verified create+stage+activity persisted (5/5)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>PO decision</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Cannot record customer follow-ups via UI</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Add activities UI to CRM customer detail</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>PO decision</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>YES — is CRM activity UI required at launch?</t>
         </is>
@@ -1334,208 +1326,208 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Additional storefront templates (5 demos)</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Mall/ecommerce/restaurant/booking/real-estate themes</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>PARTIAL — previewable, publish-blocked (fake-content themes now degrade to generic shell)</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Low — PO: reasonable deferral</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Cannot publish these themes</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Templates page</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Make tenant-configurable before publishing</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Confirm deferral</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Custom domains</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Customer-owned domain for portal</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Domain policy: subdomain first</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>PARTIAL — custom_domain_events + domains admin exist; end-to-end custom-domain flow unverified</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Low for launch</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Subdomain works as recovery route</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Domains page (WORKING)</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>Verify or defer</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Confirm deferral</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Warehouse operations</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Warehouse management module</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Unclear if in product scope</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>MISSING — no implementation found; not in customer nav</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>PO: depends on product scope — works or remove from offering</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Implement, or explicitly remove from offering/docs</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>PO decision</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>YES — does Afruheritage sell warehouse management?</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Dedicated analytics dashboards</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Advanced BI/analytics views</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Optional per PO — basic counts required</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>PARTIAL — basic operational stats exist (tenant dashboard endpoint, Sentinel analytics: real users/tenants/shipments/revenue/KYC counts); no dedicated analytics module</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>PO: basic counts suffice</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Analytics page (WORKING, real data)</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>None if basic counts acceptable</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Confirm basic-counts-only is acceptable</t>
         </is>
@@ -1594,52 +1586,52 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Native mobile app</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>iOS/Android apps</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Roadmap</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>UNSUPPORTED — responsive web only</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>PO: reasonable deferral</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>None — web works on mobile browsers</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>Post-launch/roadmap</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="J22" s="6" t="inlineStr">
         <is>
           <t>Confirm deferral</t>
         </is>
@@ -1802,156 +1794,156 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Sentinel refund/dispute</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Payment operations controls</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Depends on billing launch</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>MISSING — honest 404/501, no CP backend</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>With paid billing</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>Payments page</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>CP refund/dispute endpoints</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>With billing launch</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Runner lifecycle controls</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Restart/shutdown runtime runners</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Ops tooling</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>MISSING — honest 501, no CP backend</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Runners page (list WORKING)</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>CP runner control endpoints</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>Branded sender domain (@afruheritage.com email)</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Customer emails from platform domain</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Branding/trust; PO requirement</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>BLOCKED — provider account rejects @afruheritage.com senders; mail sends as advisory@emidentity.com; SPF strict, no DKIM, DMARC p=none</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>High for brand trust at public launch</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>Customers see non-branded sender</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>Provision sender domain + publish DKIM + tighten DMARC (ops action)</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Before public pilot</t>
         </is>
       </c>
-      <c r="J28" s="8" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1978,22 +1970,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Options</t>
         </is>
@@ -2010,7 +2002,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vendor registration + marketplace: PARTIAL — vendor identity foundation VERIFIED (membership auth, Sentinel approve/link/suspend, /me portal APIs, booking isolation). Registra</t>
+          <t>Vendor registration + marketplace: VERIFIED — 2026-10-13: full browser journey on deployed prod (P27): public /vendor/register → Sentinel approve → membership link → real invi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2050,7 +2042,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Central Afruheritage platform support: MISSING as ticket channel — public tickets require tenant_id (422 without); apex /support honestly explains tenant-routing. Help assistant +</t>
+          <t>Central Afruheritage platform support: VERIFIED — 2026-10-13: apex /support form submits platform-scope tickets (reserved afruheritage-platform tenant alias); public token trackin</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2090,7 +2082,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CRM activity history: PARTIAL — CrmActivity model + GET/POST /customers/{id}/activities endpoints exist; no UI surface for activities</t>
+          <t>CRM activity history: VERIFIED — 2026-10-13: tenant-facing /crm/customers page (create/stage/delete/expandable activity log via real crmApi); crm_customers+crm_ac</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
